--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375112</v>
+        <v>126375126</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484374</v>
+        <v>484377</v>
       </c>
       <c r="R5" t="n">
-        <v>6950890</v>
+        <v>6950876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126375126</v>
+        <v>126375112</v>
       </c>
       <c r="B6" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484377</v>
+        <v>484374</v>
       </c>
       <c r="R6" t="n">
-        <v>6950876</v>
+        <v>6950890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126375111</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126375114</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126375118</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126375126</v>
       </c>
       <c r="B5" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126375112</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126375128</v>
       </c>
       <c r="B7" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126375127</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126375113</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126375115</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126375117</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375126</v>
+        <v>126375112</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484377</v>
+        <v>484374</v>
       </c>
       <c r="R5" t="n">
-        <v>6950876</v>
+        <v>6950890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126375112</v>
+        <v>126375126</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484374</v>
+        <v>484377</v>
       </c>
       <c r="R6" t="n">
-        <v>6950890</v>
+        <v>6950876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375112</v>
+        <v>126375126</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484374</v>
+        <v>484377</v>
       </c>
       <c r="R5" t="n">
-        <v>6950890</v>
+        <v>6950876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126375126</v>
+        <v>126375112</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484377</v>
+        <v>484374</v>
       </c>
       <c r="R6" t="n">
-        <v>6950876</v>
+        <v>6950890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126375111</v>
+        <v>126375126</v>
       </c>
       <c r="B2" t="n">
-        <v>78739</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484253</v>
+        <v>484377</v>
       </c>
       <c r="R2" t="n">
-        <v>6950943</v>
+        <v>6950876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126375114</v>
+        <v>126375118</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484392</v>
+        <v>484390</v>
       </c>
       <c r="R3" t="n">
-        <v>6951050</v>
+        <v>6950884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126375118</v>
+        <v>126375128</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>78334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484390</v>
+        <v>484238</v>
       </c>
       <c r="R4" t="n">
-        <v>6950884</v>
+        <v>6950972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375126</v>
+        <v>126375111</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484377</v>
+        <v>484253</v>
       </c>
       <c r="R5" t="n">
-        <v>6950876</v>
+        <v>6950943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>126375112</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126375128</v>
+        <v>126375113</v>
       </c>
       <c r="B7" t="n">
-        <v>77929</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484238</v>
+        <v>484422</v>
       </c>
       <c r="R7" t="n">
-        <v>6950972</v>
+        <v>6951036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126375127</v>
+        <v>126375114</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484238</v>
+        <v>484392</v>
       </c>
       <c r="R8" t="n">
-        <v>6950972</v>
+        <v>6951050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126375113</v>
+        <v>126375115</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484422</v>
+        <v>484380</v>
       </c>
       <c r="R9" t="n">
-        <v>6951036</v>
+        <v>6951107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126375115</v>
+        <v>126375117</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484380</v>
+        <v>484390</v>
       </c>
       <c r="R10" t="n">
-        <v>6951107</v>
+        <v>6950884</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126375117</v>
+        <v>126375127</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484390</v>
+        <v>484238</v>
       </c>
       <c r="R11" t="n">
-        <v>6950884</v>
+        <v>6950972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 31742-2025 artfynd.xlsx
+++ b/artfynd/A 31742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375112</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375113</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375117</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375127</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>